--- a/tables/svm_per_resource_metrics.xlsx
+++ b/tables/svm_per_resource_metrics.xlsx
@@ -490,17 +490,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>0.051</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>0.101</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>0.067</t>
         </is>
       </c>
     </row>
@@ -518,17 +518,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>0.038</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.074</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>0.050</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>0.049</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.098</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>0.065</t>
         </is>
       </c>
     </row>
@@ -574,17 +574,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>0.040</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>0.074</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.052</t>
         </is>
       </c>
     </row>
@@ -602,17 +602,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>0.052</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>0.110</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.071</t>
         </is>
       </c>
     </row>
@@ -630,17 +630,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.060</t>
+          <t>0.047</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>0.091</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.080</t>
+          <t>0.062</t>
         </is>
       </c>
     </row>
@@ -658,17 +658,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>0.043</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>0.057</t>
         </is>
       </c>
     </row>
@@ -686,17 +686,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>0.024</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>0.048</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>0.031</t>
         </is>
       </c>
     </row>
@@ -714,17 +714,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>0.032</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>0.069</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>0.044</t>
         </is>
       </c>
     </row>
@@ -742,17 +742,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>0.032</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>0.064</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.070</t>
+          <t>0.042</t>
         </is>
       </c>
     </row>
@@ -770,17 +770,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.050</t>
+          <t>0.059</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>0.079</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>0.048</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.073</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>0.058</t>
         </is>
       </c>
     </row>
@@ -826,17 +826,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>0.055</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>0.106</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>0.072</t>
         </is>
       </c>
     </row>
@@ -854,17 +854,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>0.048</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>0.098</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>0.065</t>
         </is>
       </c>
     </row>

--- a/tables/svm_per_resource_metrics.xlsx
+++ b/tables/svm_per_resource_metrics.xlsx
@@ -462,17 +462,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>0.026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>0.012</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>0.017</t>
         </is>
       </c>
     </row>
@@ -518,17 +518,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.050</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>0.026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>0.038</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>0.031</t>
         </is>
       </c>
     </row>
@@ -574,17 +574,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.040</t>
+          <t>0.032</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>0.014</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>0.019</t>
         </is>
       </c>
     </row>
@@ -602,17 +602,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>0.019</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.110</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>0.014</t>
         </is>
       </c>
     </row>
@@ -630,17 +630,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>0.010</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>0.005</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>0.006</t>
         </is>
       </c>
     </row>
@@ -658,17 +658,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
@@ -686,17 +686,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
@@ -714,17 +714,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
@@ -742,17 +742,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
@@ -770,17 +770,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>0.025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.016</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
@@ -826,17 +826,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>0.016</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>0.010</t>
         </is>
       </c>
     </row>
@@ -854,17 +854,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>

--- a/tables/svm_per_resource_metrics.xlsx
+++ b/tables/svm_per_resource_metrics.xlsx
@@ -462,17 +462,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.031</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.015</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.021</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>0.035</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>0.016</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>0.022</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>0.053</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>0.077</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>0.062</t>
         </is>
       </c>
     </row>
@@ -574,17 +574,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
@@ -602,17 +602,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>0.038</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.023</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>0.029</t>
         </is>
       </c>
     </row>
@@ -630,17 +630,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.010</t>
+          <t>0.029</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.014</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.019</t>
         </is>
       </c>
     </row>
@@ -658,17 +658,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.071</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.022</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.033</t>
         </is>
       </c>
     </row>
@@ -714,17 +714,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.091</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.067</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.077</t>
         </is>
       </c>
     </row>
@@ -770,17 +770,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
@@ -826,17 +826,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>0.033</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.015</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.010</t>
+          <t>0.021</t>
         </is>
       </c>
     </row>
@@ -854,17 +854,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.018</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.010</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.013</t>
         </is>
       </c>
     </row>

--- a/tables/svm_per_resource_metrics.xlsx
+++ b/tables/svm_per_resource_metrics.xlsx
@@ -462,17 +462,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>0.026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>0.012</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>0.017</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>0.026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>0.038</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>0.031</t>
         </is>
       </c>
     </row>
@@ -574,17 +574,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.032</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.014</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.019</t>
         </is>
       </c>
     </row>
@@ -602,17 +602,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>0.019</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>0.014</t>
         </is>
       </c>
     </row>
@@ -630,17 +630,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>0.010</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>0.005</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>0.006</t>
         </is>
       </c>
     </row>
@@ -658,17 +658,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
@@ -714,17 +714,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
@@ -770,17 +770,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.016</t>
         </is>
       </c>
     </row>
@@ -826,17 +826,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>0.016</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>0.010</t>
         </is>
       </c>
     </row>
@@ -854,17 +854,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.010</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>

--- a/tables/svm_per_resource_metrics.xlsx
+++ b/tables/svm_per_resource_metrics.xlsx
@@ -419,17 +419,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Resource</t>
+          <t>Ressource</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Train Rows</t>
+          <t>Trainingszeilen</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Val Rows</t>
+          <t>Testzeilen</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
